--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E3">
         <v>0</v>
